--- a/data/trans_dic/P25C$otrosprofesionales_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otrosprofesionales_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,03</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,61</t>
+          <t>0,27; 2,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,46</t>
+          <t>0,17; 1,36</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,44</t>
+          <t>1,38; 7,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,39</t>
+          <t>0,74; 3,48</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,09</t>
+          <t>0,12; 1,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,26</t>
+          <t>0,95; 3,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,4</t>
+          <t>0,29; 1,43</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3170</t>
+          <t>0; 3481</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3119</t>
+          <t>0; 2992</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3744</t>
+          <t>0; 4372</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8102</t>
+          <t>0; 7335</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>566; 5307</t>
+          <t>555; 5188</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1170; 10937</t>
+          <t>1278; 10134</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3494</t>
+          <t>0; 3020</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1258; 7349</t>
+          <t>1204; 6772</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1429; 7600</t>
+          <t>1650; 7819</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>954; 9258</t>
+          <t>1024; 8987</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3406; 10905</t>
+          <t>3187; 11287</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4261; 16602</t>
+          <t>3480; 16944</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$otrosprofesionales_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otrosprofesionales_2023-Estudios-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>0,0; 7,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,27; 2,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,55</t>
+          <t>0,27; 2,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,36</t>
+          <t>0,47; 2,11</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,78</t>
+          <t>1,5; 8,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,48</t>
+          <t>0,82; 3,69</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,06</t>
+          <t>0,27; 1,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,37</t>
+          <t>1,02; 3,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,43</t>
+          <t>0,7; 1,86</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>669</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>646</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1315</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3481</t>
+          <t>0; 3392</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2992</t>
+          <t>0; 3321</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4372</t>
+          <t>0; 4287</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>6003</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7335</t>
+          <t>890; 8999</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>555; 5188</t>
+          <t>604; 5937</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1278; 10134</t>
+          <t>2633; 11697</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>691</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4698</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3020</t>
+          <t>0; 3634</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1204; 6772</t>
+          <t>1438; 8229</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1650; 7819</t>
+          <t>2002; 9009</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>12016</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1024; 8987</t>
+          <t>1787; 10427</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3187; 11287</t>
+          <t>3711; 12149</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3480; 16944</t>
+          <t>7141; 18988</t>
         </is>
       </c>
     </row>
